--- a/net-configurator/input/sample-2-8-9-800.xlsx
+++ b/net-configurator/input/sample-2-8-9-800.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,8 +75,13 @@
       <sz val="16"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font/>
   </fonts>
-  <fills count="14">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -150,6 +155,19 @@
         <fgColor rgb="FFDAEEF3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid"/>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -203,7 +221,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -393,6 +411,15 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -760,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.85546875" customWidth="1" style="25" min="1" max="1"/>
@@ -1795,146 +1822,310 @@
       <c r="E48" s="50" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="44" t="inlineStr">
+      <c r="A49" s="64" t="inlineStr">
+        <is>
+          <t>OPENSHIFT</t>
+        </is>
+      </c>
+      <c r="B49" s="64" t="n"/>
+      <c r="C49" s="64" t="n"/>
+      <c r="D49" s="64" t="n"/>
+      <c r="E49" s="64" t="n"/>
+      <c r="F49" s="64" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="65" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="B50" s="65" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C50" s="65" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D50" s="65" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="E50" s="65" t="inlineStr">
+        <is>
+          <t>Default Value</t>
+        </is>
+      </c>
+      <c r="F50" s="65" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="66" t="inlineStr">
+        <is>
+          <t>ocp_cluster_domain</t>
+        </is>
+      </c>
+      <c r="B51" s="66" t="inlineStr">
+        <is>
+          <t>era.example.com</t>
+        </is>
+      </c>
+      <c r="C51" s="66" t="inlineStr">
+        <is>
+          <t>Base domain for the OpenShift Container Platform cluster (e.g. api.&lt;cluster_name&gt;.&lt;domain&gt; and *.apps.&lt;cluster_name&gt;.&lt;domain&gt;)</t>
+        </is>
+      </c>
+      <c r="D51" s="66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E51" s="66" t="inlineStr">
+        <is>
+          <t>era.example.com</t>
+        </is>
+      </c>
+      <c r="F51" s="66" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="66" t="inlineStr">
+        <is>
+          <t>ocp_version</t>
+        </is>
+      </c>
+      <c r="B52" s="66" t="inlineStr">
+        <is>
+          <t>4.22.0</t>
+        </is>
+      </c>
+      <c r="C52" s="66" t="inlineStr">
+        <is>
+          <t>OpenShift Container Platform version for Agent-Based Installer (ABI). Match the openshift-install binary version used with make generate-ocp-iso.</t>
+        </is>
+      </c>
+      <c r="D52" s="66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E52" s="66" t="inlineStr">
+        <is>
+          <t>4.22.0</t>
+        </is>
+      </c>
+      <c r="F52" s="66" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="66" t="inlineStr">
+        <is>
+          <t>ocp_api_vip</t>
+        </is>
+      </c>
+      <c r="B53" s="66" t="n"/>
+      <c r="C53" s="66" t="inlineStr">
+        <is>
+          <t>API Virtual IP — must be an unused IP in the cluster machine network subnet. Leave blank to derive automatically (last usable IP in support subnet).</t>
+        </is>
+      </c>
+      <c r="D53" s="66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E53" s="66" t="n"/>
+      <c r="F53" s="66" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="66" t="inlineStr">
+        <is>
+          <t>ocp_ingress_vip</t>
+        </is>
+      </c>
+      <c r="B54" s="66" t="n"/>
+      <c r="C54" s="66" t="inlineStr">
+        <is>
+          <t>Ingress Virtual IP — must be an unused IP in the cluster machine network subnet distinct from ocp_api_vip. Leave blank to derive automatically.</t>
+        </is>
+      </c>
+      <c r="D54" s="66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E54" s="66" t="n"/>
+      <c r="F54" s="66" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="66" t="inlineStr">
+        <is>
+          <t>ocp_oem</t>
+        </is>
+      </c>
+      <c r="B55" s="66" t="inlineStr">
+        <is>
+          <t>dell</t>
+        </is>
+      </c>
+      <c r="C55" s="66" t="inlineStr">
+        <is>
+          <t>Server OEM vendor — used to select the correct root device hint for the Agent-Based Installer install disk. Valid values: dell, hpe, lenovo.</t>
+        </is>
+      </c>
+      <c r="D55" s="66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E55" s="66" t="inlineStr">
+        <is>
+          <t>dell</t>
+        </is>
+      </c>
+      <c r="F55" s="66" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="44" t="inlineStr">
         <is>
           <t>VERSIONS</t>
         </is>
       </c>
-      <c r="B49" s="32" t="n"/>
-      <c r="C49" s="31" t="n"/>
-      <c r="D49" s="31" t="n"/>
-      <c r="E49" s="51" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="45" t="inlineStr">
+      <c r="B57" s="32" t="n"/>
+      <c r="C57" s="31" t="n"/>
+      <c r="D57" s="31" t="n"/>
+      <c r="E57" s="51" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="45" t="inlineStr">
         <is>
           <t>Switch Function</t>
         </is>
       </c>
-      <c r="B50" s="45" t="inlineStr">
+      <c r="B58" s="45" t="inlineStr">
         <is>
           <t>Cumulus Version</t>
         </is>
       </c>
-      <c r="C50" s="45" t="inlineStr">
+      <c r="C58" s="45" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D50" s="45" t="inlineStr">
+      <c r="D58" s="45" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="E50" s="48" t="inlineStr">
+      <c r="E58" s="48" t="inlineStr">
         <is>
           <t>Default Value</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="27" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="27" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="B51" s="46" t="inlineStr">
+      <c r="B59" s="46" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
       </c>
-      <c r="C51" s="27" t="inlineStr">
+      <c r="C59" s="27" t="inlineStr">
         <is>
           <t>Cumulus Linux version (5.16+ supported in this release)</t>
         </is>
       </c>
-      <c r="D51" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E51" s="54" t="inlineStr">
+      <c r="D59" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E59" s="54" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="27" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="27" t="inlineStr">
         <is>
           <t>oob</t>
         </is>
       </c>
-      <c r="B52" s="46" t="inlineStr">
+      <c r="B60" s="46" t="inlineStr">
         <is>
           <t>5.15.1</t>
         </is>
       </c>
-      <c r="C52" s="27" t="inlineStr">
+      <c r="C60" s="27" t="inlineStr">
         <is>
           <t>Cumulus Linux version (5.15+ supported in this release)</t>
         </is>
       </c>
-      <c r="D52" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E52" s="54" t="inlineStr">
+      <c r="D60" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E60" s="54" t="inlineStr">
         <is>
           <t>5.15.1</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="27" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="27" t="inlineStr">
         <is>
           <t>csl</t>
         </is>
       </c>
-      <c r="B53" s="46" t="inlineStr">
+      <c r="B61" s="46" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
       </c>
-      <c r="C53" s="27" t="inlineStr">
+      <c r="C61" s="27" t="inlineStr">
         <is>
           <t>Cumulus Linux version (5.16+ supported in this release)</t>
         </is>
       </c>
-      <c r="D53" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E53" s="54" t="inlineStr">
+      <c r="D61" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E61" s="54" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="27" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="27" t="inlineStr">
         <is>
           <t>gsl</t>
         </is>
       </c>
-      <c r="B54" s="46" t="inlineStr">
+      <c r="B62" s="46" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
       </c>
-      <c r="C54" s="27" t="inlineStr">
+      <c r="C62" s="27" t="inlineStr">
         <is>
           <t>Cumulus Linux version (5.16+ supported in this release)</t>
         </is>
       </c>
-      <c r="D54" s="36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="E54" s="54" t="inlineStr">
+      <c r="D62" s="36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="E62" s="54" t="inlineStr">
         <is>
           <t>5.16.1</t>
         </is>
